--- a/healthcare_assessment_forms/003_neck_pain_assessment_quiz--healthcare_assessment_forms.xlsx
+++ b/healthcare_assessment_forms/003_neck_pain_assessment_quiz--healthcare_assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -941,8 +941,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -970,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'mild'}</t>
+          <t>mild</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Mild'}</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'moderate'}</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Moderate'}</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'severe'}</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Severe'}</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'less_than_a_day'}</t>
+          <t>less_than_a_day</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Less than a day'}</t>
+          <t>Less than a day</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'1-4_days'}</t>
+          <t>1-4_days</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': '1-4 days'}</t>
+          <t>1-4 days</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'5-7_days'}</t>
+          <t>5-7_days</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': '5-7 days'}</t>
+          <t>5-7 days</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'more_than_7_days'}</t>
+          <t>more_than_7_days</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'More than 7 days'}</t>
+          <t>More than 7 days</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'front_of_neck'}</t>
+          <t>front_of_neck</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Front of neck'}</t>
+          <t>Front of neck</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'back_of_neck'}</t>
+          <t>back_of_neck</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Back of neck'}</t>
+          <t>Back of neck</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'sides_of_neck'}</t>
+          <t>sides_of_neck</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Sides of neck'}</t>
+          <t>Sides of neck</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'slight'}</t>
+          <t>slight</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Slight'}</t>
+          <t>Slight</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'moderate'}</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Moderate'}</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'severe'}</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Severe'}</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'physical_therapy'}</t>
+          <t>physical_therapy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Physical therapy'}</t>
+          <t>Physical therapy</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'pain_management'}</t>
+          <t>pain_management</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Pain management'}</t>
+          <t>Pain management</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'rest_and_relaxation'}</t>
+          <t>rest_and_relaxation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Rest and relaxation'}</t>
+          <t>Rest and relaxation</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'medication'}</t>
+          <t>medication</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Medication'}</t>
+          <t>Medication</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1276,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'surgery'}</t>
+          <t>surgery</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Surgery'}</t>
+          <t>Surgery</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1327,12 +1327,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'family_history_of_neck_pain'}</t>
+          <t>family_history_of_neck_pain</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Family history of neck pain'}</t>
+          <t>Family history of neck pain</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'family_history_of_other_medical_condition'}</t>
+          <t>family_history_of_other_medical_condition</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Family history of other medical condition'}</t>
+          <t>Family history of other medical condition</t>
         </is>
       </c>
     </row>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'family_history_of_other'}</t>
+          <t>family_history_of_other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Family history of other'}</t>
+          <t>Family history of other</t>
         </is>
       </c>
     </row>
